--- a/labs/lab-12-end-to-end-campaign-orchestrator/data/orchestrator_runs.xlsx
+++ b/labs/lab-12-end-to-end-campaign-orchestrator/data/orchestrator_runs.xlsx
@@ -734,7 +734,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acceptance check: A successful run reaches PUBLISHED_DRY_RUN only after research, strategy, content, QA and approval succeed; failures stop downstream execution.</t>
+          <t>Acceptance check: A successful run reaches SOCIALPOST_REQUEST_INSPECTED only after research, strategy, content, QA and approval succeed; failures stop downstream execution.</t>
         </is>
       </c>
     </row>
